--- a/reports/2026-09_月次実績報告/excel/第51期下期松江営業所担当者別実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期下期松江営業所担当者別実績.xlsx
@@ -5761,7 +5761,7 @@
         <v>70.3</v>
       </c>
       <c r="P66" s="39" t="n">
-        <v>148.74</v>
+        <v>146.42</v>
       </c>
       <c r="Q66" s="39" t="n">
         <v>30.8</v>
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>15047.04</v>
+        <v>15030.357</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>10820.014</v>
@@ -18122,13 +18122,13 @@
         <v/>
       </c>
       <c r="L65" s="1" t="n">
-        <v>4536.348</v>
+        <v>4530.822</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>3567.44</v>
       </c>
       <c r="N65" s="86" t="n">
-        <v>3002.952</v>
+        <v>3003.121</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>3520.407</v>
@@ -18184,7 +18184,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>15265.922</v>
+        <v>14753.872</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>10070.893</v>
@@ -18206,19 +18206,19 @@
         <v/>
       </c>
       <c r="L66" s="1" t="n">
-        <v>3492.024</v>
+        <v>3444.2879</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2365.03</v>
+        <v>2452.33</v>
       </c>
       <c r="N66" s="86" t="n">
-        <v>2676.518</v>
+        <v>2672.198</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>3549.9651</v>
+        <v>3549.9051</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>2620.623</v>
+        <v>2618.323</v>
       </c>
       <c r="Q66" s="2" t="n">
         <v>2735.5196</v>
@@ -18268,16 +18268,16 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10061</v>
+        <v>10590.23</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>8724</v>
+        <v>8723.672</v>
       </c>
       <c r="G67" s="86" t="n">
         <v>8649.739</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>11910.007</v>
+        <v>11950.588</v>
       </c>
       <c r="I67" s="2" t="n">
         <v>10792.559</v>
@@ -18290,16 +18290,16 @@
         <v/>
       </c>
       <c r="L67" s="1" t="n">
-        <v>2538</v>
+        <v>2588.803</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2281</v>
+        <v>2281.164</v>
       </c>
       <c r="N67" s="86" t="n">
-        <v>2121.064</v>
+        <v>2181.163</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>3025.832</v>
+        <v>3066.413</v>
       </c>
       <c r="P67" s="2" t="n">
         <v>2924.322</v>
